--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.72964379165187</v>
+        <v>4.343567116143428</v>
       </c>
       <c r="D2" t="n">
-        <v>25.83711844115754</v>
+        <v>4.198531746688101</v>
       </c>
       <c r="E2" t="n">
-        <v>8.41215064283705</v>
+        <v>1.366974479461021</v>
       </c>
       <c r="F2" t="n">
-        <v>8.652212477241893</v>
+        <v>1.405984527551808</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.628931364327</v>
+        <v>5.627201346703138</v>
       </c>
       <c r="D3" t="n">
-        <v>34.70294199467148</v>
+        <v>5.639228074134115</v>
       </c>
       <c r="E3" t="n">
-        <v>8.41215064283705</v>
+        <v>1.366974479461021</v>
       </c>
       <c r="F3" t="n">
-        <v>8.652212477241893</v>
+        <v>1.405984527551808</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.72315262744945</v>
+        <v>4.830012301960537</v>
       </c>
       <c r="D4" t="n">
-        <v>29.72232942516485</v>
+        <v>4.829878531589288</v>
       </c>
       <c r="E4" t="n">
-        <v>8.41215064283705</v>
+        <v>1.366974479461021</v>
       </c>
       <c r="F4" t="n">
-        <v>8.652212477241893</v>
+        <v>1.405984527551808</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>42.57197627732982</v>
+        <v>6.917946145066096</v>
       </c>
       <c r="D5" t="n">
-        <v>33.50895882291444</v>
+        <v>5.445205808723597</v>
       </c>
       <c r="E5" t="n">
-        <v>8.41215064283705</v>
+        <v>1.366974479461021</v>
       </c>
       <c r="F5" t="n">
-        <v>8.652212477241893</v>
+        <v>1.405984527551808</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.16590724000572</v>
+        <v>4.90195992650093</v>
       </c>
       <c r="D6" t="n">
-        <v>29.36451723048773</v>
+        <v>4.771734049954256</v>
       </c>
       <c r="E6" t="n">
-        <v>8.41215064283705</v>
+        <v>1.366974479461021</v>
       </c>
       <c r="F6" t="n">
-        <v>8.652212477241893</v>
+        <v>1.405984527551808</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.77515159835077</v>
+        <v>7.438462134732</v>
       </c>
       <c r="D7" t="n">
-        <v>45.71760873270782</v>
+        <v>7.429111419065022</v>
       </c>
       <c r="E7" t="n">
-        <v>8.41215064283705</v>
+        <v>1.366974479461021</v>
       </c>
       <c r="F7" t="n">
-        <v>8.652212477241893</v>
+        <v>1.405984527551808</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>53.9389611762134</v>
+        <v>8.765081191134678</v>
       </c>
       <c r="D8" t="n">
-        <v>53.86903124169847</v>
+        <v>8.753717576776001</v>
       </c>
       <c r="E8" t="n">
-        <v>8.41215064283705</v>
+        <v>1.366974479461021</v>
       </c>
       <c r="F8" t="n">
-        <v>8.652212477241893</v>
+        <v>1.405984527551808</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.77609925769099</v>
+        <v>7.113616129374786</v>
       </c>
       <c r="D9" t="n">
-        <v>44.37129932730669</v>
+        <v>7.210336140687337</v>
       </c>
       <c r="E9" t="n">
-        <v>8.41215064283705</v>
+        <v>1.366974479461021</v>
       </c>
       <c r="F9" t="n">
-        <v>8.652212477241893</v>
+        <v>1.405984527551808</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.58231945950871</v>
+        <v>6.432126912170165</v>
       </c>
       <c r="D10" t="n">
-        <v>39.66028393774243</v>
+        <v>6.444796139883146</v>
       </c>
       <c r="E10" t="n">
-        <v>8.41215064283705</v>
+        <v>1.366974479461021</v>
       </c>
       <c r="F10" t="n">
-        <v>8.652212477241893</v>
+        <v>1.405984527551808</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
